--- a/ValueSet-carotid-imaging-modality-vs.xlsx
+++ b/ValueSet-carotid-imaging-modality-vs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-30T10:04:33+00:00</t>
+    <t>2026-02-09T10:35:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,10 +111,10 @@
     <t>Doppler ultrasonography of carotid arteries (procedure)</t>
   </si>
   <si>
-    <t>419949007</t>
-  </si>
-  <si>
-    <t>Computed tomography angiography of intracranial artery with contrast (procedure)</t>
+    <t>396205005</t>
+  </si>
+  <si>
+    <t>Computed tomography of brain without radiopaque contrast (procedure)</t>
   </si>
   <si>
     <t>1366357009</t>

--- a/ValueSet-carotid-imaging-modality-vs.xlsx
+++ b/ValueSet-carotid-imaging-modality-vs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T10:35:12+00:00</t>
+    <t>2026-10-27T13:25:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-carotid-imaging-modality-vs.xlsx
+++ b/ValueSet-carotid-imaging-modality-vs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:25:43+00:00</t>
+    <t>2026-10-27T13:28:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
